--- a/data/saeop/노년사회화교육.xlsx
+++ b/data/saeop/노년사회화교육.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J69"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -2541,9 +2541,169 @@
         <v/>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>O</v>
+      </c>
+      <c r="B65" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E65" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F65" t="str">
+        <v>건강관리실</v>
+      </c>
+      <c r="G65" t="str">
+        <v>건강관리실.jpg</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>O</v>
+      </c>
+      <c r="B66" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E66" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F66" t="str">
+        <v>당구실</v>
+      </c>
+      <c r="G66" t="str">
+        <v>당구실.jpg</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>O</v>
+      </c>
+      <c r="B67" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E67" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F67" t="str">
+        <v>포켓볼실</v>
+      </c>
+      <c r="G67" t="str">
+        <v>포켓볼실.jpg</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>O</v>
+      </c>
+      <c r="B68" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E68" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F68" t="str">
+        <v>장기바둑실</v>
+      </c>
+      <c r="G68" t="str">
+        <v>장기바둑실.jpg</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>O</v>
+      </c>
+      <c r="B69" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E69" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F69" t="str">
+        <v>탁구실</v>
+      </c>
+      <c r="G69" t="str">
+        <v>탁구실.jpg</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/노년사회화교육.xlsx
+++ b/data/saeop/노년사회화교육.xlsx
@@ -2590,10 +2590,10 @@
         <v>사진</v>
       </c>
       <c r="F66" t="str">
-        <v>당구실</v>
+        <v>장기바둑실</v>
       </c>
       <c r="G66" t="str">
-        <v>당구실.jpg</v>
+        <v>장기바둑실.jpg</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -2654,10 +2654,10 @@
         <v>사진</v>
       </c>
       <c r="F68" t="str">
-        <v>장기바둑실</v>
+        <v>당구실</v>
       </c>
       <c r="G68" t="str">
-        <v>장기바둑실.jpg</v>
+        <v>당구실.jpg</v>
       </c>
       <c r="H68" t="str">
         <v/>

--- a/data/saeop/노년사회화교육.xlsx
+++ b/data/saeop/노년사회화교육.xlsx
@@ -2590,10 +2590,10 @@
         <v>사진</v>
       </c>
       <c r="F66" t="str">
-        <v>장기바둑실</v>
+        <v>탁구실</v>
       </c>
       <c r="G66" t="str">
-        <v>장기바둑실.jpg</v>
+        <v>탁구실.jpg</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -2686,10 +2686,10 @@
         <v>사진</v>
       </c>
       <c r="F69" t="str">
-        <v>탁구실</v>
+        <v>장기바둑실</v>
       </c>
       <c r="G69" t="str">
-        <v>탁구실.jpg</v>
+        <v>장기바둑실.jpg</v>
       </c>
       <c r="H69" t="str">
         <v/>

--- a/data/saeop/노년사회화교육.xlsx
+++ b/data/saeop/노년사회화교육.xlsx
@@ -2558,10 +2558,10 @@
         <v>사진</v>
       </c>
       <c r="F65" t="str">
-        <v>건강관리실</v>
+        <v>탁구실</v>
       </c>
       <c r="G65" t="str">
-        <v>건강관리실.jpg</v>
+        <v>탁구실.jpg</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -2590,10 +2590,10 @@
         <v>사진</v>
       </c>
       <c r="F66" t="str">
-        <v>탁구실</v>
+        <v>포켓볼실</v>
       </c>
       <c r="G66" t="str">
-        <v>탁구실.jpg</v>
+        <v>포켓볼실.jpg</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -2622,10 +2622,10 @@
         <v>사진</v>
       </c>
       <c r="F67" t="str">
-        <v>포켓볼실</v>
+        <v>당구실</v>
       </c>
       <c r="G67" t="str">
-        <v>포켓볼실.jpg</v>
+        <v>당구실.jpg</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -2654,10 +2654,10 @@
         <v>사진</v>
       </c>
       <c r="F68" t="str">
-        <v>당구실</v>
+        <v>장기바둑실</v>
       </c>
       <c r="G68" t="str">
-        <v>당구실.jpg</v>
+        <v>장기바둑실.jpg</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -2686,10 +2686,10 @@
         <v>사진</v>
       </c>
       <c r="F69" t="str">
-        <v>장기바둑실</v>
+        <v>건강관리실</v>
       </c>
       <c r="G69" t="str">
-        <v>장기바둑실.jpg</v>
+        <v>건강관리실.jpg</v>
       </c>
       <c r="H69" t="str">
         <v/>

--- a/data/saeop/노년사회화교육.xlsx
+++ b/data/saeop/노년사회화교육.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J65"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -2558,10 +2558,10 @@
         <v>사진</v>
       </c>
       <c r="F65" t="str">
-        <v>탁구실</v>
+        <v>건강관리실</v>
       </c>
       <c r="G65" t="str">
-        <v>탁구실.jpg</v>
+        <v>건강관리실.jpg</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -2570,140 +2570,12 @@
         <v/>
       </c>
       <c r="J65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>O</v>
-      </c>
-      <c r="B66" t="str">
-        <v>nonyeon</v>
-      </c>
-      <c r="C66" t="str">
-        <v/>
-      </c>
-      <c r="D66" t="str">
-        <v>자율이용프로그램</v>
-      </c>
-      <c r="E66" t="str">
-        <v>사진</v>
-      </c>
-      <c r="F66" t="str">
-        <v>포켓볼실</v>
-      </c>
-      <c r="G66" t="str">
-        <v>포켓볼실.jpg</v>
-      </c>
-      <c r="H66" t="str">
-        <v/>
-      </c>
-      <c r="I66" t="str">
-        <v/>
-      </c>
-      <c r="J66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>O</v>
-      </c>
-      <c r="B67" t="str">
-        <v>nonyeon</v>
-      </c>
-      <c r="C67" t="str">
-        <v/>
-      </c>
-      <c r="D67" t="str">
-        <v>자율이용프로그램</v>
-      </c>
-      <c r="E67" t="str">
-        <v>사진</v>
-      </c>
-      <c r="F67" t="str">
-        <v>당구실</v>
-      </c>
-      <c r="G67" t="str">
-        <v>당구실.jpg</v>
-      </c>
-      <c r="H67" t="str">
-        <v/>
-      </c>
-      <c r="I67" t="str">
-        <v/>
-      </c>
-      <c r="J67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>O</v>
-      </c>
-      <c r="B68" t="str">
-        <v>nonyeon</v>
-      </c>
-      <c r="C68" t="str">
-        <v/>
-      </c>
-      <c r="D68" t="str">
-        <v>자율이용프로그램</v>
-      </c>
-      <c r="E68" t="str">
-        <v>사진</v>
-      </c>
-      <c r="F68" t="str">
-        <v>장기바둑실</v>
-      </c>
-      <c r="G68" t="str">
-        <v>장기바둑실.jpg</v>
-      </c>
-      <c r="H68" t="str">
-        <v/>
-      </c>
-      <c r="I68" t="str">
-        <v/>
-      </c>
-      <c r="J68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>O</v>
-      </c>
-      <c r="B69" t="str">
-        <v>nonyeon</v>
-      </c>
-      <c r="C69" t="str">
-        <v/>
-      </c>
-      <c r="D69" t="str">
-        <v>자율이용프로그램</v>
-      </c>
-      <c r="E69" t="str">
-        <v>사진</v>
-      </c>
-      <c r="F69" t="str">
-        <v>건강관리실</v>
-      </c>
-      <c r="G69" t="str">
-        <v>건강관리실.jpg</v>
-      </c>
-      <c r="H69" t="str">
-        <v/>
-      </c>
-      <c r="I69" t="str">
-        <v/>
-      </c>
-      <c r="J69" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J65"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/노년사회화교육.xlsx
+++ b/data/saeop/노년사회화교육.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J70"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -2573,9 +2573,169 @@
         <v/>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>O</v>
+      </c>
+      <c r="B66" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E66" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F66" t="str">
+        <v>포켓볼실</v>
+      </c>
+      <c r="G66" t="str">
+        <v>포켓볼실.jpg</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>O</v>
+      </c>
+      <c r="B67" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E67" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F67" t="str">
+        <v>탁구실</v>
+      </c>
+      <c r="G67" t="str">
+        <v>탁구실.jpg</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>O</v>
+      </c>
+      <c r="B68" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E68" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F68" t="str">
+        <v>당구실</v>
+      </c>
+      <c r="G68" t="str">
+        <v>당구실.jpg</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>O</v>
+      </c>
+      <c r="B69" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E69" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F69" t="str">
+        <v>스마트테이블</v>
+      </c>
+      <c r="G69" t="str">
+        <v>스마트테이블.jpg</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>O</v>
+      </c>
+      <c r="B70" t="str">
+        <v>nonyeon</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>자율이용프로그램</v>
+      </c>
+      <c r="E70" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F70" t="str">
+        <v>장기바둑실</v>
+      </c>
+      <c r="G70" t="str">
+        <v>장기바둑실.jpg</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J70"/>
   </ignoredErrors>
 </worksheet>
 </file>